--- a/accord/data/hotel_data.xlsx
+++ b/accord/data/hotel_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC8"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -684,26 +684,6 @@
           <t>hotel_contrat_type_manage</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>hotel_brand_ibis_budget</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>hotel_brand_ibis_styles</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>hotel_brand_mercure</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>hotel_brand_novotel</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -727,10 +707,8 @@
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06200</t>
-        </is>
+      <c r="F2" t="n">
+        <v>6200</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -764,9 +742,7 @@
       <c r="P2" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -791,9 +767,7 @@
       <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
@@ -803,9 +777,7 @@
       <c r="AC2" t="n">
         <v>4</v>
       </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
         <v>10.2</v>
       </c>
@@ -833,27 +805,19 @@
       <c r="AM2" t="n">
         <v>3</v>
       </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
         <v>1</v>
       </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="n">
         <v>0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
       <c r="AU2" t="n">
         <v>1</v>
       </c>
@@ -867,18 +831,6 @@
         <v>1</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -904,10 +856,8 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>67000</t>
-        </is>
+      <c r="F3" t="n">
+        <v>67000</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -941,9 +891,7 @@
       <c r="P3" t="n">
         <v>0.8</v>
       </c>
-      <c r="Q3" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -968,9 +916,7 @@
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
@@ -980,9 +926,7 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
         <v>0.4</v>
       </c>
@@ -1010,27 +954,19 @@
       <c r="AM3" t="n">
         <v>2</v>
       </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN3" t="inlineStr"/>
       <c r="AO3" t="n">
         <v>1</v>
       </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
         <v>1</v>
       </c>
       <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
       <c r="AU3" t="n">
         <v>1</v>
       </c>
@@ -1044,18 +980,6 @@
         <v>1</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1081,10 +1005,8 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>95700</t>
-        </is>
+      <c r="F4" t="n">
+        <v>95700</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -1118,9 +1040,7 @@
       <c r="P4" t="n">
         <v>0.98</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="n">
         <v>1</v>
       </c>
@@ -1145,9 +1065,7 @@
       <c r="Y4" t="n">
         <v>1</v>
       </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
@@ -1157,9 +1075,7 @@
       <c r="AC4" t="n">
         <v>1</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
         <v>20</v>
       </c>
@@ -1187,27 +1103,19 @@
       <c r="AM4" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
         <v>1</v>
       </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="n">
         <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
       <c r="AU4" t="n">
         <v>1</v>
       </c>
@@ -1221,18 +1129,6 @@
         <v>1</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1258,10 +1154,8 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>92100</t>
-        </is>
+      <c r="F5" t="n">
+        <v>92100</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1295,9 +1189,7 @@
       <c r="P5" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1322,9 +1214,7 @@
       <c r="Y5" t="n">
         <v>2</v>
       </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
         <v>1</v>
       </c>
@@ -1334,9 +1224,7 @@
       <c r="AC5" t="n">
         <v>13</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
         <v>10.2</v>
       </c>
@@ -1364,27 +1252,19 @@
       <c r="AM5" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="n">
         <v>1</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
       <c r="AU5" t="n">
         <v>0</v>
       </c>
@@ -1398,18 +1278,6 @@
         <v>1</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1435,10 +1303,8 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>75018</t>
-        </is>
+      <c r="F6" t="n">
+        <v>75018</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1472,9 +1338,7 @@
       <c r="P6" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1499,9 +1363,7 @@
       <c r="Y6" t="n">
         <v>1</v>
       </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
@@ -1511,9 +1373,7 @@
       <c r="AC6" t="n">
         <v>1</v>
       </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
         <v>10.2</v>
       </c>
@@ -1541,27 +1401,19 @@
       <c r="AM6" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="n">
         <v>1</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
       <c r="AU6" t="n">
         <v>0</v>
       </c>
@@ -1576,18 +1428,6 @@
       </c>
       <c r="AY6" t="n">
         <v>1</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1616,10 +1456,8 @@
           <t>LE DOMAINE DE MEZTIVA</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>74120</t>
-        </is>
+      <c r="F7" t="n">
+        <v>74120</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1653,9 +1491,7 @@
       <c r="P7" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1680,9 +1516,7 @@
       <c r="Y7" t="n">
         <v>1</v>
       </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="n">
         <v>1</v>
       </c>
@@ -1692,9 +1526,7 @@
       <c r="AC7" t="n">
         <v>3</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
         <v>10.2</v>
       </c>
@@ -1722,27 +1554,19 @@
       <c r="AM7" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="n">
         <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
       <c r="AU7" t="n">
         <v>0</v>
       </c>
@@ -1757,18 +1581,6 @@
       </c>
       <c r="AY7" t="n">
         <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1793,10 +1605,8 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>75015</t>
-        </is>
+      <c r="F8" t="n">
+        <v>75015</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -1830,9 +1640,7 @@
       <c r="P8" t="n">
         <v>0.89</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1857,9 +1665,7 @@
       <c r="Y8" t="n">
         <v>3</v>
       </c>
-      <c r="Z8" t="n">
-        <v>0</v>
-      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="n">
         <v>1</v>
       </c>
@@ -1869,9 +1675,7 @@
       <c r="AC8" t="n">
         <v>36</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
         <v>10.2</v>
       </c>
@@ -1899,27 +1703,19 @@
       <c r="AM8" t="n">
         <v>2.5</v>
       </c>
-      <c r="AN8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
-      <c r="AP8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="n">
         <v>0</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
       </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
@@ -1933,18 +1729,6 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
         <v>1</v>
       </c>
     </row>

--- a/accord/data/hotel_data.xlsx
+++ b/accord/data/hotel_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,257 +417,257 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>hotel_code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>hotel_name</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>hotel_brand</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>hotel_adresse_postale_1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>hotel_adresse_postale_2</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>hotel_code_postal</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>hotel_city</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>hotel_lat</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>hotel_lon</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>hotel_contrat_signe_annee</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hotel_derniere_reno</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>hotel_lobby_derniere_reno</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>hotel_nb_chambres</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>hotel_to_annuel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>hotel_to_le_plus_bas_taux</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>hotel_to_le_plus_haut_taux</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_assises</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_bouilloire</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_fontaine_a_eau</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_machine_a_cafe</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_micro_ondes</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>hotel_dispo_dans_lobby_vitrine_refrigeree</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>hotel_f_b_bar</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>hotel_f_b_minibar</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>hotel_f_b_restaurant</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>hotel_f_b_room_service</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_piscine</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_salle_de_sport</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_salles_de_reunion</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>hotel_non_f_b_spa</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>hotel_affaires_pct</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>hotel_loisirs_pct</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_amis</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_couples</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>hotel_loisirs_top_1_familles</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>hotel_international_pct</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>hotel_national_pct</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_existe_deja</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>hotel_corner_de_vente_actuel_metres_lineaires</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_caisse_code_barres</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_distributeur_auto</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_frigo_connecte</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_reception</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_f_b_snacking_comptoir</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_armoire_connectee</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_caisse_code_barres</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_distributeur_auto</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>hotel_corner_actuel_offre_non_f_b_reception</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>hotel_metres_lineaires_dedies_corner</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>hotel_contrat_type_franchise</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>hotel_contrat_type_manage</t>
         </is>
@@ -721,27 +709,15 @@
       <c r="I2" t="n">
         <v>7.240512</v>
       </c>
-      <c r="J2" t="n">
-        <v>2003.666666666667</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="L2" t="n">
-        <v>2020</v>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>129</v>
       </c>
-      <c r="N2" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>0</v>
@@ -778,12 +754,8 @@
         <v>4</v>
       </c>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="n">
         <v>1</v>
       </c>
@@ -793,12 +765,8 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
@@ -1100,9 +1068,7 @@
       <c r="AL4" t="n">
         <v>1</v>
       </c>
-      <c r="AM4" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="AM4" t="inlineStr"/>
       <c r="AN4" t="inlineStr"/>
       <c r="AO4" t="n">
         <v>1</v>
@@ -1168,27 +1134,15 @@
       <c r="I5" t="n">
         <v>2.256274</v>
       </c>
-      <c r="J5" t="n">
-        <v>2003.666666666667</v>
-      </c>
-      <c r="K5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2020</v>
-      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
         <v>191</v>
       </c>
-      <c r="N5" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="n">
         <v>0</v>
@@ -1225,12 +1179,8 @@
         <v>13</v>
       </c>
       <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
         <v>0</v>
       </c>
@@ -1240,18 +1190,12 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
-      <c r="AM5" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="inlineStr"/>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1317,27 +1261,15 @@
       <c r="I6" t="n">
         <v>2.329923</v>
       </c>
-      <c r="J6" t="n">
-        <v>2003.666666666667</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2020</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2020</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
         <v>305</v>
       </c>
-      <c r="N6" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="n">
         <v>0</v>
@@ -1374,12 +1306,8 @@
         <v>1</v>
       </c>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="n">
         <v>0</v>
       </c>
@@ -1389,18 +1317,12 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="n">
         <v>1</v>
       </c>
-      <c r="AM6" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="AM6" t="inlineStr"/>
       <c r="AN6" t="inlineStr"/>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1470,27 +1392,15 @@
       <c r="I7" t="n">
         <v>6.6190552711</v>
       </c>
-      <c r="J7" t="n">
-        <v>2003.666666666667</v>
-      </c>
-      <c r="K7" t="n">
-        <v>2020</v>
-      </c>
-      <c r="L7" t="n">
-        <v>2020</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="n">
         <v>572</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="n">
         <v>0</v>
@@ -1527,12 +1437,8 @@
         <v>3</v>
       </c>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
@@ -1542,18 +1448,12 @@
       <c r="AI7" t="n">
         <v>1</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
-      <c r="AM7" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="AM7" t="inlineStr"/>
       <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1622,24 +1522,14 @@
       <c r="J8" t="n">
         <v>1976</v>
       </c>
-      <c r="K8" t="n">
-        <v>2020</v>
-      </c>
-      <c r="L8" t="n">
-        <v>2020</v>
-      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="n">
         <v>764</v>
       </c>
-      <c r="N8" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.89</v>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="n">
         <v>0</v>
@@ -1676,12 +1566,8 @@
         <v>36</v>
       </c>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>0</v>
-      </c>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
@@ -1691,18 +1577,12 @@
       <c r="AI8" t="n">
         <v>1</v>
       </c>
-      <c r="AJ8" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>35.3</v>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
       <c r="AL8" t="n">
         <v>1</v>
       </c>
-      <c r="AM8" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="AM8" t="inlineStr"/>
       <c r="AN8" t="inlineStr"/>
       <c r="AO8" t="n">
         <v>1</v>
